--- a/data/trans_dic/IP31KM09_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM09_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>91,63%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>95,32; 100,0</t>
+          <t>74,59; 93,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>75,95; 93,69</t>
+          <t>93,52; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87,19; 96,18</t>
+          <t>85,28; 95,47</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>89,38; 94,15</t>
+          <t>87,37; 96,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>84,84; 96,29</t>
+          <t>88,76; 93,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88,88; 94,46</t>
+          <t>88,86; 94,33</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>93,05%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>89,65; 96,42</t>
+          <t>87,82; 95,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87,26; 95,03</t>
+          <t>90,49; 96,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,98; 95,03</t>
+          <t>90,42; 95,15</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,98; 94,58</t>
+          <t>88,43; 94,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>86,42; 94,63</t>
+          <t>90,77; 94,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89,68; 94,07</t>
+          <t>90,56; 94,07</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>66</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53173</t>
+          <t>45970</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50287</t>
+          <t>45309</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>103460</t>
+          <t>91279</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>51184; 53699</t>
+          <t>40065; 50040</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>44311; 54664</t>
+          <t>42929; 45905</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>97686; 107764</t>
+          <t>84959; 95106</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>569</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>415421</t>
+          <t>437575</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>472655</t>
+          <t>388643</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>888076</t>
+          <t>826219</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>403863; 425383</t>
+          <t>407512; 448896</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>428646; 486487</t>
+          <t>376954; 397298</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>850618; 904039</t>
+          <t>791807; 840526</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>208</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>137366</t>
+          <t>153312</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>166369</t>
+          <t>138699</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>303734</t>
+          <t>292010</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>131053; 140949</t>
+          <t>146389; 158503</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>158056; 172140</t>
+          <t>133144; 142504</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>294515; 311053</t>
+          <t>283772; 298619</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>879</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>843</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>879</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>605960</t>
+          <t>636857</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>689310</t>
+          <t>572651</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1295270</t>
+          <t>1209508</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>592939; 616407</t>
+          <t>607353; 650829</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>643635; 704732</t>
+          <t>560716; 582171</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1252343; 1313636</t>
+          <t>1181449; 1227226</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM09_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM09_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que desayunan cereales o derivados (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>85,58%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>98,7%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>91,63%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>74,59; 93,16</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>93,52; 100,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>85,28; 95,47</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>93,82%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>91,52%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>92,72%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>87,37; 96,24</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>88,76; 93,56</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>88,86; 94,33</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>91,98%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>94,26%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>93,05%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>87,82; 95,09</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>90,49; 96,85</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>90,42; 95,15</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>92,72%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>92,71%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>92,72%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>88,43; 94,76</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>90,77; 94,25</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>90,56; 94,07</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.8558130586286414</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.9870152373871665</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.9162711720053693</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>45970</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>45309</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>91279</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.7458783242330925</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.9351774550362381</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.8528331800974229</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>40065; 50040</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>42929; 45905</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>84959; 95106</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.9315762326190313</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.9546843139248634</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>569</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1167</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.9381508790725529</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.9151735890765565</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.9272005981035657</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>437575</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>388643</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>826219</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.8736961202461778</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.8876472659075902</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.888582782722474</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>407512; 448896</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>376954; 397298</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>791807; 840526</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.9624224389103075</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.9355544540559396</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.9432554805004604</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.9197646838144204</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.9426318715825052</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.9304861631777758</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>153312</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>138699</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>292010</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.8782314239742081</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.904876408729217</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.9042353465513646</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>146389; 158503</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>133144; 142504</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>283772; 298619</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.9509059588795924</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.9684946210538048</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.9515476818265433</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>879</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>843</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1722</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.9272492928201883</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.9270530609013345</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.9271563749325041</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>636857</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>572651</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1209508</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.8842917752124185</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.9077322740226088</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.9056472845870819</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>607353; 650829</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>560716; 582171</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>1181449; 1227226</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.9475922409419725</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.9424647800056631</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.940738016682076</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que desayunan cereales o derivados (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>45970</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>45309</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>91279</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>40065</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>42929</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>84959</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>50040</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>45905</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>95106</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>598</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>569</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>437575</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>388643</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>826219</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>407512</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>376954</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>791807</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>448896</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>397298</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>840526</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>214</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>208</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>153312</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>138699</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>292010</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>146389</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>133144</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>283772</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>158503</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>142504</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>298619</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>879</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>843</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>636857</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>572651</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>1209508</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>607353</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>560716</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>1181449</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>650829</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>582171</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>1227226</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>